--- a/data/trans_dic/IP2906_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida</t>
+          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida (tasa de respuesta: 98,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,04; 49,95</t>
+          <t>28,54; 49,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,65; 55,79</t>
+          <t>33,23; 56,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,95; 50,12</t>
+          <t>34,8; 49,88</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,52; 54,37</t>
+          <t>40,76; 54,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,53; 52,96</t>
+          <t>40,49; 52,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,65; 51,97</t>
+          <t>42,56; 51,73</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,82; 46,87</t>
+          <t>33,75; 46,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,06; 48,26</t>
+          <t>34,84; 47,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,96; 45,19</t>
+          <t>36,24; 45,5</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,12; 49,4</t>
+          <t>37,25; 49,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,94; 47,09</t>
+          <t>34,13; 47,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,24; 46,63</t>
+          <t>37,97; 47,06</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,09; 46,81</t>
+          <t>39,98; 46,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,55; 46,41</t>
+          <t>39,13; 46,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,47; 45,43</t>
+          <t>40,09; 45,5</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida (tasa de respuesta: 98,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>18731</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20191</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>38922</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>13637; 23786</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15193; 25603</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>32537; 46638</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>76046</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>84338</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>160384</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>64423; 86247</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>73305; 95640</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>144321; 175403</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>68782</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>88181</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>156963</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>57889; 80381</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>74031; 101682</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139152; 174728</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>104762</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>122832</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>227594</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>89563; 118892</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>102312; 142444</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205092; 254194</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>268322</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>315541</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>583863</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>246961; 290031</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>289224; 343369</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>543972; 617390</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2906_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,54; 49,79</t>
+          <t>28,88; 49,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,23; 56,0</t>
+          <t>32,91; 55,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,8; 49,88</t>
+          <t>34,19; 50,35</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,76; 54,57</t>
+          <t>41,31; 54,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,49; 52,83</t>
+          <t>40,4; 52,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,56; 51,73</t>
+          <t>42,52; 51,4</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,75; 46,86</t>
+          <t>33,57; 46,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,84; 47,85</t>
+          <t>34,98; 47,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,24; 45,5</t>
+          <t>35,87; 45,69</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,25; 49,45</t>
+          <t>37,98; 49,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,13; 47,52</t>
+          <t>34,3; 47,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,97; 47,06</t>
+          <t>37,43; 46,44</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,98; 46,95</t>
+          <t>40,0; 46,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39,13; 46,46</t>
+          <t>39,33; 46,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,09; 45,5</t>
+          <t>40,65; 45,64</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13637; 23786</t>
+          <t>13796; 23792</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15193; 25603</t>
+          <t>15046; 25183</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32537; 46638</t>
+          <t>31969; 47074</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64423; 86247</t>
+          <t>65293; 86753</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73305; 95640</t>
+          <t>73150; 95750</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>144321; 175403</t>
+          <t>144189; 174302</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>57889; 80381</t>
+          <t>57590; 80408</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74031; 101682</t>
+          <t>74326; 101320</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139152; 174728</t>
+          <t>137751; 175477</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89563; 118892</t>
+          <t>91311; 118628</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102312; 142444</t>
+          <t>102837; 141819</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>205092; 254194</t>
+          <t>202198; 250863</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>246961; 290031</t>
+          <t>247107; 288013</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>289224; 343369</t>
+          <t>290695; 342775</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>543972; 617390</t>
+          <t>551504; 619270</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2906_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,23%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,88; 49,8</t>
+          <t>32,8; 55,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,91; 55,08</t>
+          <t>29,34; 49,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,19; 50,35</t>
+          <t>33,48; 49,43</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,31; 54,89</t>
+          <t>41,52; 54,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,4; 52,89</t>
+          <t>41,88; 54,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,52; 51,4</t>
+          <t>43,21; 52,26</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,57; 46,88</t>
+          <t>36,96; 50,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,98; 47,68</t>
+          <t>33,57; 46,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,87; 45,69</t>
+          <t>36,83; 46,13</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>43,5%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,98; 49,34</t>
+          <t>35,06; 47,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,3; 47,31</t>
+          <t>40,27; 51,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,43; 46,44</t>
+          <t>39,09; 48,09</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,0; 46,62</t>
+          <t>39,61; 47,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39,33; 46,38</t>
+          <t>40,6; 47,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,65; 45,64</t>
+          <t>41,44; 46,23</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18731</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>17154</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38922</t>
+          <t>33664</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13796; 23792</t>
+          <t>12401; 20804</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15046; 25183</t>
+          <t>12860; 21911</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31969; 47074</t>
+          <t>27332; 40353</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>123</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>76046</t>
+          <t>74665</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>84338</t>
+          <t>69654</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160384</t>
+          <t>144319</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65293; 86753</t>
+          <t>64899; 84470</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73150; 95750</t>
+          <t>60427; 79057</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>144189; 174302</t>
+          <t>129874; 157074</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>91</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68782</t>
+          <t>86730</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88181</t>
+          <t>68721</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156963</t>
+          <t>155451</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>57590; 80408</t>
+          <t>73961; 100280</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74326; 101320</t>
+          <t>58109; 80131</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>137751; 175477</t>
+          <t>137458; 172180</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>151</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>104762</t>
+          <t>120543</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>122832</t>
+          <t>110778</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>227594</t>
+          <t>231321</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>91311; 118628</t>
+          <t>100661; 137121</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102837; 141819</t>
+          <t>98532; 125196</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>202198; 250863</t>
+          <t>207875; 255724</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>401</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>268322</t>
+          <t>298448</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>315541</t>
+          <t>266306</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>583863</t>
+          <t>564755</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>247107; 288013</t>
+          <t>269880; 323279</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>290695; 342775</t>
+          <t>245993; 285743</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>551504; 619270</t>
+          <t>533428; 595068</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2906_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida (tasa de respuesta: 98,82%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>43,67%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>39,13%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>41,23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>32,8; 55,02</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>29,34; 49,99</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>33,48; 49,43</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>47,77%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>48,27%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>48,01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>41,52; 54,04</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>41,88; 54,79</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>43,21; 52,26</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>43,34%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>39,7%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>41,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>36,96; 50,11</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>33,57; 46,29</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>36,83; 46,13</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>41,99%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>45,27%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>43,5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>35,06; 47,76</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>40,27; 51,17</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>39,09; 48,09</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>43,8%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>43,95%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>43,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>39,61; 47,45</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>40,6; 47,16</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>41,44; 46,23</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.4366654287002027</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.3913488235307725</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.4123358382846344</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>16510</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>17154</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>33664</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.3279884361201624</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.2933827868154941</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.3347884842903879</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>12401; 20804</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12860; 21911</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>27332; 40353</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.5502129661928965</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.4998839579422562</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.4942767516237723</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.4776995288584369</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4827381501072439</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.4801181606340848</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>74665</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>69654</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>144319</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4152163828977126</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.4187942894059384</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.4320630421690512</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>64899; 84470</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>60427; 79057</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>129874; 157074</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.5404298619506687</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.5479046544186206</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.5225535748820114</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.4333771556379777</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.3969899402375553</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.4165006306630116</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>86730</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>68721</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>155451</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.3695712267958106</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.3356852435068598</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.3682903121574994</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>73961; 100280</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>58109; 80131</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>137458; 172180</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5010835995895264</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.4629002945783777</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.4613206446993973</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.4198587885075035</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4527323789670223</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.4349845625129812</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>120543</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>110778</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>231321</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.3506081420164794</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4026847124782976</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.3908953212744889</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>100661; 137121</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>98532; 125196</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>207875; 255724</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.4776001255975927</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.511656116850559</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.4808734204640215</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>814</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.4380309296072232</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.4395120082384555</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.438728077316637</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>298448</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>266306</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>564755</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.3961016589335272</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.405987134212531</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.4143918140926462</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>269880; 323279</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>245993; 285743</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>533428; 595068</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.4744745965083328</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.471590512930327</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.4622767947937819</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida (tasa de respuesta: 98,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>16510</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>17154</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>33664</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>12401</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>12860</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>27332</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>20804</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>21911</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>40353</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>131</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>123</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>74665</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>69654</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>144319</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>64899</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>60427</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>129874</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>84470</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>79057</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>157074</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>86730</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>68721</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>155451</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>73961</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>58109</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>137458</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>100280</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>80131</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>172180</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>143</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>151</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>120543</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>110778</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>231321</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>100661</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>98532</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>207875</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>137121</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>125196</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>255724</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>413</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>401</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>298448</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>266306</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>564755</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>269880</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>245993</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>533428</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>323279</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>285743</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>595068</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>